--- a/Data_2025_v3.xlsx
+++ b/Data_2025_v3.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\IPS\송원산업\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{256CD3E0-4884-4A48-9B68-C405F278C6A4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59375AA-0A8C-4568-BA23-B678885D962D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data_20240930" sheetId="1" r:id="rId1"/>
+    <sheet name="Data_20251031" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -114,31 +114,6 @@
             <charset val="129"/>
           </rPr>
           <t>금리</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>2019.04~ ICE BofA GBMI 사용(인포맥스)</t>
         </r>
         <r>
           <rPr>
@@ -586,260 +561,8 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>소비자심리지수</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> from  </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>한국은행</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> "</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>소비자동향조사</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">". </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>인포맥스에는</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> '</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>소비자동향지수</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>'</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>만</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>있음경기선행</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">, </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>동행지지수로</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>변경도</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>무방
-인경</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">: </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>인포맥스</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>경기동행지수로</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>변경</t>
+          <t>지표누리 www.index.go.kr
+소비자동향지수(CSI)</t>
         </r>
       </text>
     </comment>
@@ -906,7 +629,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">'. </t>
+          <t xml:space="preserve">' </t>
         </r>
         <r>
           <rPr>
@@ -917,7 +640,7 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>전체</t>
+          <t>연도별로</t>
         </r>
         <r>
           <rPr>
@@ -938,7 +661,7 @@
             <family val="3"/>
             <charset val="129"/>
           </rPr>
-          <t>임금총액기준</t>
+          <t>대체</t>
         </r>
         <r>
           <rPr>
@@ -948,60 +671,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>인상률</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>수치</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>기입</t>
+          <t xml:space="preserve">(2025~)
+</t>
         </r>
         <r>
           <rPr>
@@ -2212,7 +1883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE74"/>
+  <dimension ref="A1:AE80"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.5" style="1" bestFit="1" customWidth="1"/>
@@ -2277,7 +1948,7 @@
       <c r="K1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>10</v>
       </c>
       <c r="M1" s="7" t="s">
@@ -2471,6 +2142,7 @@
         <v>1.3541295901382533E-2</v>
       </c>
       <c r="M3" s="4">
+        <f t="shared" ref="M3:M66" si="0">X3/X2-1</f>
         <v>-7.3448327501940081E-2</v>
       </c>
       <c r="N3" s="4">
@@ -2566,6 +2238,7 @@
         <v>2.2171601911126881E-2</v>
       </c>
       <c r="M4" s="4">
+        <f t="shared" si="0"/>
         <v>4.3531497644166084E-2</v>
       </c>
       <c r="N4" s="4">
@@ -2661,7 +2334,8 @@
         <v>-2.7787573896966844E-3</v>
       </c>
       <c r="M5" s="4">
-        <v>-4.9783631055749018E-2</v>
+        <f t="shared" si="0"/>
+        <v>-4.9783631055749011E-2</v>
       </c>
       <c r="N5" s="4">
         <v>9.81</v>
@@ -2756,6 +2430,7 @@
         <v>2.0334967138772475E-2</v>
       </c>
       <c r="M6" s="4">
+        <f t="shared" si="0"/>
         <v>-2.8035859820700892E-2</v>
       </c>
       <c r="N6" s="4">
@@ -2851,6 +2526,7 @@
         <v>-1.0171581038785904E-2</v>
       </c>
       <c r="M7" s="4">
+        <f t="shared" si="0"/>
         <v>4.8409637207222467E-2</v>
       </c>
       <c r="N7" s="4">
@@ -2946,6 +2622,7 @@
         <v>6.6588675153038679E-3</v>
       </c>
       <c r="M8" s="4">
+        <f t="shared" si="0"/>
         <v>9.9028137951091555E-3</v>
       </c>
       <c r="N8" s="4">
@@ -3041,6 +2718,7 @@
         <v>-7.5826476995126679E-3</v>
       </c>
       <c r="M9" s="4">
+        <f t="shared" si="0"/>
         <v>2.1502486224969086E-3</v>
       </c>
       <c r="N9" s="4">
@@ -3136,6 +2814,7 @@
         <v>5.83167520010619E-3</v>
       </c>
       <c r="M10" s="4">
+        <f t="shared" si="0"/>
         <v>5.2544110040422254E-2</v>
       </c>
       <c r="N10" s="4">
@@ -3231,6 +2910,7 @@
         <v>1.2765619796462957E-2</v>
       </c>
       <c r="M11" s="4">
+        <f t="shared" si="0"/>
         <v>-3.5792452916042827E-2</v>
       </c>
       <c r="N11" s="4">
@@ -3258,7 +2938,7 @@
         <v>105.3</v>
       </c>
       <c r="V11" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>3.7000000000000005E-2</v>
       </c>
       <c r="W11" s="4">
         <v>260.10514999999998</v>
@@ -3326,6 +3006,7 @@
         <v>6.7251636906773271E-3</v>
       </c>
       <c r="M12" s="4">
+        <f t="shared" si="0"/>
         <v>-6.229324071146447E-2</v>
       </c>
       <c r="N12" s="4">
@@ -3353,7 +3034,7 @@
         <v>98</v>
       </c>
       <c r="V12" s="5">
-        <v>3.9E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="W12" s="4">
         <v>263.49943000000002</v>
@@ -3421,6 +3102,7 @@
         <v>6.8547628470037258E-2</v>
       </c>
       <c r="M13" s="4">
+        <f t="shared" si="0"/>
         <v>-0.11694455488397137</v>
       </c>
       <c r="N13" s="4">
@@ -3448,7 +3130,7 @@
         <v>79.7</v>
       </c>
       <c r="V13" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>3.7000000000000005E-2</v>
       </c>
       <c r="W13" s="4">
         <v>260.48397</v>
@@ -3516,7 +3198,8 @@
         <v>8.4645637379347383E-2</v>
       </c>
       <c r="M14" s="4">
-        <v>0.10994847946017415</v>
+        <f t="shared" si="0"/>
+        <v>0.10994847946017416</v>
       </c>
       <c r="N14" s="4">
         <v>17.010000000000002</v>
@@ -3543,7 +3226,7 @@
         <v>72.099999999999994</v>
       </c>
       <c r="V14" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>3.7000000000000005E-2</v>
       </c>
       <c r="W14" s="4">
         <v>261.40607</v>
@@ -3611,6 +3294,7 @@
         <v>7.1773299732019735E-2</v>
       </c>
       <c r="M15" s="4">
+        <f t="shared" si="0"/>
         <v>4.2124504508205041E-2</v>
       </c>
       <c r="N15" s="4">
@@ -3638,7 +3322,7 @@
         <v>78.8</v>
       </c>
       <c r="V15" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>3.7000000000000005E-2</v>
       </c>
       <c r="W15" s="4">
         <v>263.98065000000003</v>
@@ -3706,6 +3390,7 @@
         <v>6.3151230329221653E-2</v>
       </c>
       <c r="M16" s="4">
+        <f t="shared" si="0"/>
         <v>3.8790894757587679E-2</v>
       </c>
       <c r="N16" s="4">
@@ -3733,7 +3418,7 @@
         <v>83.1</v>
       </c>
       <c r="V16" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>3.6000000000000004E-2</v>
       </c>
       <c r="W16" s="4">
         <v>263.53223000000003</v>
@@ -3801,6 +3486,7 @@
         <v>6.8256152090303557E-2</v>
       </c>
       <c r="M17" s="4">
+        <f t="shared" si="0"/>
         <v>6.6896548453041049E-2</v>
       </c>
       <c r="N17" s="4">
@@ -3828,7 +3514,7 @@
         <v>85.4</v>
       </c>
       <c r="V17" s="5">
-        <v>3.7000000000000005E-2</v>
+        <v>3.6000000000000004E-2</v>
       </c>
       <c r="W17" s="4">
         <v>265.28187000000003</v>
@@ -3896,6 +3582,7 @@
         <v>3.5202579731033801E-2</v>
       </c>
       <c r="M18" s="4">
+        <f t="shared" si="0"/>
         <v>3.4142893343469538E-2</v>
       </c>
       <c r="N18" s="4">
@@ -3923,7 +3610,7 @@
         <v>89.3</v>
       </c>
       <c r="V18" s="5">
-        <v>3.7000000000000005E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="W18" s="4">
         <v>263.00882999999999</v>
@@ -3991,6 +3678,7 @@
         <v>4.5004666240974434E-2</v>
       </c>
       <c r="M19" s="4">
+        <f t="shared" si="0"/>
         <v>7.39412854606325E-4</v>
       </c>
       <c r="N19" s="4">
@@ -4018,7 +3706,7 @@
         <v>80.7</v>
       </c>
       <c r="V19" s="5">
-        <v>3.4000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="W19" s="4">
         <v>264.83888999999999</v>
@@ -4086,6 +3774,7 @@
         <v>4.5635920957170839E-2</v>
       </c>
       <c r="M20" s="4">
+        <f t="shared" si="0"/>
         <v>-2.6092298175600992E-2</v>
       </c>
       <c r="N20" s="4">
@@ -4113,7 +3802,7 @@
         <v>92.7</v>
       </c>
       <c r="V20" s="5">
-        <v>3.3000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="W20" s="4">
         <v>263.80329999999998</v>
@@ -4181,6 +3870,7 @@
         <v>5.3928979398298438E-2</v>
       </c>
       <c r="M21" s="4">
+        <f t="shared" si="0"/>
         <v>0.14299450852391771</v>
       </c>
       <c r="N21" s="4">
@@ -4208,7 +3898,7 @@
         <v>99.1</v>
       </c>
       <c r="V21" s="5">
-        <v>3.3000000000000002E-2</v>
+        <v>3.1E-2</v>
       </c>
       <c r="W21" s="4">
         <v>262.94783999999999</v>
@@ -4276,6 +3966,7 @@
         <v>5.9159669054087427E-2</v>
       </c>
       <c r="M22" s="4">
+        <f t="shared" si="0"/>
         <v>0.10887417320768389</v>
       </c>
       <c r="N22" s="4">
@@ -4303,7 +3994,7 @@
         <v>91</v>
       </c>
       <c r="V22" s="5">
-        <v>3.2000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="W22" s="4">
         <v>262.4273</v>
@@ -4371,6 +4062,7 @@
         <v>3.2709572676496546E-2</v>
       </c>
       <c r="M23" s="4">
+        <f t="shared" si="0"/>
         <v>3.5754679881815354E-2</v>
       </c>
       <c r="N23" s="4">
@@ -4398,7 +4090,7 @@
         <v>95.3</v>
       </c>
       <c r="V23" s="5">
-        <v>3.3000000000000002E-2</v>
+        <v>2.8999999999999998E-2</v>
       </c>
       <c r="W23" s="4">
         <v>262.39595000000003</v>
@@ -4466,6 +4158,7 @@
         <v>1.3457621948484988E-3</v>
       </c>
       <c r="M24" s="4">
+        <f t="shared" si="0"/>
         <v>1.2344559019692669E-2</v>
       </c>
       <c r="N24" s="4">
@@ -4493,7 +4186,7 @@
         <v>97.4</v>
       </c>
       <c r="V24" s="5">
-        <v>3.4000000000000002E-2</v>
+        <v>3.1E-2</v>
       </c>
       <c r="W24" s="4">
         <v>260.60768999999999</v>
@@ -4561,6 +4254,7 @@
         <v>1.2573843248920857E-2</v>
       </c>
       <c r="M25" s="4">
+        <f t="shared" si="0"/>
         <v>1.6087223485288682E-2</v>
       </c>
       <c r="N25" s="4">
@@ -4588,7 +4282,7 @@
         <v>100.6</v>
       </c>
       <c r="V25" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="W25" s="4">
         <v>259.55058000000002</v>
@@ -4656,6 +4350,7 @@
         <v>3.886002618567197E-4</v>
       </c>
       <c r="M26" s="4">
+        <f t="shared" si="0"/>
         <v>2.8235263374512432E-2</v>
       </c>
       <c r="N26" s="4">
@@ -4683,7 +4378,7 @@
         <v>102.4</v>
       </c>
       <c r="V26" s="5">
-        <v>4.2999999999999997E-2</v>
+        <v>4.0999999999999995E-2</v>
       </c>
       <c r="W26" s="4">
         <v>258.99459999999999</v>
@@ -4751,6 +4446,7 @@
         <v>-6.6457261722396854E-4</v>
       </c>
       <c r="M27" s="4">
+        <f t="shared" si="0"/>
         <v>1.7808924157999284E-2</v>
       </c>
       <c r="N27" s="4">
@@ -4778,7 +4474,7 @@
         <v>105.5</v>
       </c>
       <c r="V27" s="5">
-        <v>4.2999999999999997E-2</v>
+        <v>4.0999999999999995E-2</v>
       </c>
       <c r="W27" s="4">
         <v>258.58593999999999</v>
@@ -4846,6 +4542,7 @@
         <v>-2.9627435004808689E-4</v>
       </c>
       <c r="M28" s="4">
+        <f t="shared" si="0"/>
         <v>2.8952033758645523E-2</v>
       </c>
       <c r="N28" s="4">
@@ -4873,7 +4570,7 @@
         <v>110.8</v>
       </c>
       <c r="V28" s="5">
-        <v>4.2999999999999997E-2</v>
+        <v>4.0999999999999995E-2</v>
       </c>
       <c r="W28" s="4">
         <v>259.30891000000003</v>
@@ -4941,6 +4638,7 @@
         <v>-3.2197729181981938E-4</v>
       </c>
       <c r="M29" s="4">
+        <f t="shared" si="0"/>
         <v>-2.8622735600664861E-2</v>
       </c>
       <c r="N29" s="4">
@@ -4968,7 +4666,7 @@
         <v>103.6</v>
       </c>
       <c r="V29" s="5">
-        <v>4.2999999999999997E-2</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="W29" s="4">
         <v>262.40667999999999</v>
@@ -5036,6 +4734,7 @@
         <v>5.3627685809016779E-3</v>
       </c>
       <c r="M30" s="4">
+        <f t="shared" si="0"/>
         <v>-9.5243448499848782E-4</v>
       </c>
       <c r="N30" s="4">
@@ -5063,7 +4762,7 @@
         <v>102.8</v>
       </c>
       <c r="V30" s="5">
-        <v>4.2999999999999997E-2</v>
+        <v>4.0999999999999995E-2</v>
       </c>
       <c r="W30" s="4">
         <v>262.60892000000001</v>
@@ -5131,7 +4830,8 @@
         <v>-9.0304461757206855E-3</v>
       </c>
       <c r="M31" s="4">
-        <v>-4.0774926780171687E-2</v>
+        <f t="shared" si="0"/>
+        <v>-4.0774926780171694E-2</v>
       </c>
       <c r="N31" s="4">
         <v>24.67</v>
@@ -5158,7 +4858,7 @@
         <v>104.1</v>
       </c>
       <c r="V31" s="5">
-        <v>4.0999999999999995E-2</v>
+        <v>0.04</v>
       </c>
       <c r="W31" s="4">
         <v>258.97994</v>
@@ -5226,6 +4926,7 @@
         <v>-9.4961736006374808E-3</v>
       </c>
       <c r="M32" s="4">
+        <f t="shared" si="0"/>
         <v>-3.1979718588904027E-2</v>
       </c>
       <c r="N32" s="4">
@@ -5253,7 +4954,7 @@
         <v>107.3</v>
       </c>
       <c r="V32" s="5">
-        <v>4.0999999999999995E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="W32" s="4">
         <v>254.56572</v>
@@ -5321,6 +5022,7 @@
         <v>-8.5628144226892466E-3</v>
       </c>
       <c r="M33" s="4">
+        <f t="shared" si="0"/>
         <v>-4.4323185263979825E-2</v>
       </c>
       <c r="N33" s="4">
@@ -5348,7 +5050,7 @@
         <v>108.2</v>
       </c>
       <c r="V33" s="5">
-        <v>3.9E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="W33" s="4">
         <v>259.22557</v>
@@ -5416,6 +5118,7 @@
         <v>-1.5835818154790626E-2</v>
       </c>
       <c r="M34" s="4">
+        <f t="shared" si="0"/>
         <v>4.8833924501850978E-2</v>
       </c>
       <c r="N34" s="4">
@@ -5443,7 +5146,7 @@
         <v>104.3</v>
       </c>
       <c r="V34" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>3.6000000000000004E-2</v>
       </c>
       <c r="W34" s="4">
         <v>258.8537</v>
@@ -5511,7 +5214,8 @@
         <v>-2.6969001047083552E-2</v>
       </c>
       <c r="M35" s="4">
-        <v>-0.10555639514382144</v>
+        <f t="shared" si="0"/>
+        <v>-0.10555639514382142</v>
       </c>
       <c r="N35" s="4">
         <v>23.27</v>
@@ -5606,6 +5310,7 @@
         <v>-2.2942780430841636E-2</v>
       </c>
       <c r="M36" s="4">
+        <f t="shared" si="0"/>
         <v>1.3456787342209342E-2</v>
       </c>
       <c r="N36" s="4">
@@ -5701,6 +5406,7 @@
         <v>-4.1183489429061249E-2</v>
       </c>
       <c r="M37" s="4">
+        <f t="shared" si="0"/>
         <v>2.1662134426011059E-2</v>
       </c>
       <c r="N37" s="4">
@@ -5796,6 +5502,7 @@
         <v>-7.2613128391461279E-2</v>
       </c>
       <c r="M38" s="4">
+        <f t="shared" si="0"/>
         <v>-2.2700487734121366E-2</v>
       </c>
       <c r="N38" s="4">
@@ -5823,7 +5530,7 @@
         <v>104.3</v>
       </c>
       <c r="V38" s="5">
-        <v>5.2000000000000005E-2</v>
+        <v>5.4000000000000006E-2</v>
       </c>
       <c r="W38" s="4">
         <v>247.84097</v>
@@ -5891,6 +5598,7 @@
         <v>-7.6810673632917936E-2</v>
       </c>
       <c r="M39" s="4">
+        <f t="shared" si="0"/>
         <v>-3.395113263204852E-3</v>
       </c>
       <c r="N39" s="4">
@@ -5918,7 +5626,7 @@
         <v>103.1</v>
       </c>
       <c r="V39" s="5">
-        <v>5.4000000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="W39" s="4">
         <v>247.92716999999999</v>
@@ -5986,6 +5694,7 @@
         <v>-9.6187300881677484E-2</v>
       </c>
       <c r="M40" s="4">
+        <f t="shared" si="0"/>
         <v>-0.13152388398674564</v>
       </c>
       <c r="N40" s="4">
@@ -6013,7 +5722,7 @@
         <v>96.8</v>
       </c>
       <c r="V40" s="5">
-        <v>5.4000000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="W40" s="4">
         <v>243.60401999999999</v>
@@ -6081,6 +5790,7 @@
         <v>-8.3659074339221595E-2</v>
       </c>
       <c r="M41" s="4">
+        <f t="shared" si="0"/>
         <v>5.0955140956169931E-2</v>
       </c>
       <c r="N41" s="4">
@@ -6108,7 +5818,7 @@
         <v>86.2</v>
       </c>
       <c r="V41" s="5">
-        <v>5.2999999999999999E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="W41" s="4">
         <v>249.91591</v>
@@ -6176,6 +5886,7 @@
         <v>-0.10878699145008242</v>
       </c>
       <c r="M42" s="4">
+        <f t="shared" si="0"/>
         <v>8.3826228839487538E-3</v>
       </c>
       <c r="N42" s="4">
@@ -6203,7 +5914,7 @@
         <v>89</v>
       </c>
       <c r="V42" s="5">
-        <v>5.2999999999999999E-2</v>
+        <v>5.4000000000000006E-2</v>
       </c>
       <c r="W42" s="4">
         <v>243.20891</v>
@@ -6271,6 +5982,7 @@
         <v>-0.13283135208845931</v>
       </c>
       <c r="M43" s="4">
+        <f t="shared" si="0"/>
         <v>-0.12805566230456522</v>
       </c>
       <c r="N43" s="4">
@@ -6298,7 +6010,7 @@
         <v>91.6</v>
       </c>
       <c r="V43" s="5">
-        <v>5.2000000000000005E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="W43" s="4">
         <v>239.21207000000001</v>
@@ -6366,6 +6078,7 @@
         <v>-0.13645605463822352</v>
       </c>
       <c r="M44" s="4">
+        <f t="shared" si="0"/>
         <v>6.4078237430932328E-2</v>
       </c>
       <c r="N44" s="4">
@@ -6393,7 +6106,7 @@
         <v>89</v>
       </c>
       <c r="V44" s="5">
-        <v>5.0999999999999997E-2</v>
+        <v>5.2000000000000005E-2</v>
       </c>
       <c r="W44" s="4">
         <v>237.54911999999999</v>
@@ -6461,6 +6174,7 @@
         <v>-0.11829515887117914</v>
       </c>
       <c r="M45" s="4">
+        <f t="shared" si="0"/>
         <v>7.8008031007887224E-2</v>
       </c>
       <c r="N45" s="4">
@@ -6556,6 +6270,7 @@
         <v>-0.12509403228194882</v>
       </c>
       <c r="M46" s="4">
+        <f t="shared" si="0"/>
         <v>-9.550136904304507E-2</v>
       </c>
       <c r="N46" s="4">
@@ -6651,7 +6366,8 @@
         <v>-8.7945212086136593E-2</v>
       </c>
       <c r="M47" s="4">
-        <v>8.436773385798603E-2</v>
+        <f t="shared" si="0"/>
+        <v>8.4367733857986016E-2</v>
       </c>
       <c r="N47" s="4">
         <v>9.17</v>
@@ -6746,6 +6462,7 @@
         <v>-9.1786361649513593E-2</v>
       </c>
       <c r="M48" s="4">
+        <f t="shared" si="0"/>
         <v>-5.0431325976875163E-3</v>
       </c>
       <c r="N48" s="4">
@@ -6841,6 +6558,7 @@
         <v>-4.9140294979347687E-2</v>
       </c>
       <c r="M49" s="4">
+        <f t="shared" si="0"/>
         <v>2.6528793750129509E-2</v>
       </c>
       <c r="N49" s="4">
@@ -6868,7 +6586,7 @@
         <v>92</v>
       </c>
       <c r="V49" s="5">
-        <v>4.9000000000000002E-2</v>
+        <v>0.05</v>
       </c>
       <c r="W49" s="4">
         <v>252.78292999999999</v>
@@ -6936,6 +6654,7 @@
         <v>-1.5104893302358757E-2</v>
       </c>
       <c r="M50" s="4">
+        <f t="shared" si="0"/>
         <v>9.960191532827789E-3</v>
       </c>
       <c r="N50" s="4">
@@ -6963,7 +6682,7 @@
         <v>95.2</v>
       </c>
       <c r="V50" s="5">
-        <v>0.05</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="W50" s="4">
         <v>253.64605</v>
@@ -7031,6 +6750,7 @@
         <v>-1.8580371736644619E-2</v>
       </c>
       <c r="M51" s="4">
+        <f t="shared" si="0"/>
         <v>3.0217506885785728E-2</v>
       </c>
       <c r="N51" s="4">
@@ -7058,7 +6778,7 @@
         <v>98.1</v>
       </c>
       <c r="V51" s="5">
-        <v>0.05</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="W51" s="4">
         <v>251.97920999999999</v>
@@ -7126,6 +6846,7 @@
         <v>-5.7940315245156304E-3</v>
       </c>
       <c r="M52" s="4">
+        <f t="shared" si="0"/>
         <v>-4.9823058297633338E-3</v>
       </c>
       <c r="N52" s="4">
@@ -7153,7 +6874,7 @@
         <v>100.8</v>
       </c>
       <c r="V52" s="5">
-        <v>0.05</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="W52" s="4">
         <v>251.32856000000001</v>
@@ -7221,6 +6942,7 @@
         <v>-3.1787114523720406E-2</v>
       </c>
       <c r="M53" s="4">
+        <f t="shared" si="0"/>
         <v>2.6635156847146124E-2</v>
       </c>
       <c r="N53" s="4">
@@ -7248,7 +6970,7 @@
         <v>103.4</v>
       </c>
       <c r="V53" s="5">
-        <v>4.9000000000000002E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="W53" s="4">
         <v>251.85529</v>
@@ -7316,6 +7038,7 @@
         <v>-4.9548140710135025E-3</v>
       </c>
       <c r="M54" s="4">
+        <f t="shared" si="0"/>
         <v>-2.898677343138667E-2</v>
       </c>
       <c r="N54" s="4">
@@ -7343,7 +7066,7 @@
         <v>103.3</v>
       </c>
       <c r="V54" s="5">
-        <v>4.9000000000000002E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="W54" s="4">
         <v>252.15873999999999</v>
@@ -7411,6 +7134,7 @@
         <v>1.3147729059694635E-2</v>
       </c>
       <c r="M55" s="4">
+        <f t="shared" si="0"/>
         <v>-3.5676982478376584E-2</v>
       </c>
       <c r="N55" s="4">
@@ -7438,7 +7162,7 @@
         <v>99.8</v>
       </c>
       <c r="V55" s="5">
-        <v>4.8000000000000001E-2</v>
+        <v>4.4000000000000004E-2</v>
       </c>
       <c r="W55" s="4">
         <v>250.80067</v>
@@ -7506,6 +7230,7 @@
         <v>9.8029106257775389E-3</v>
       </c>
       <c r="M56" s="4">
+        <f t="shared" si="0"/>
         <v>-7.5892368168044011E-2</v>
       </c>
       <c r="N56" s="4">
@@ -7533,7 +7258,7 @@
         <v>98.2</v>
       </c>
       <c r="V56" s="5">
-        <v>4.7E-2</v>
+        <v>4.4000000000000004E-2</v>
       </c>
       <c r="W56" s="4">
         <v>248.89739</v>
@@ -7601,7 +7326,8 @@
         <v>1.8568401633591414E-2</v>
       </c>
       <c r="M57" s="4">
-        <v>0.11295045193350293</v>
+        <f t="shared" si="0"/>
+        <v>0.11295045193350295</v>
       </c>
       <c r="N57" s="4">
         <v>11.91</v>
@@ -7628,7 +7354,7 @@
         <v>97.3</v>
       </c>
       <c r="V57" s="5">
-        <v>4.5999999999999999E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="W57" s="4">
         <v>256.68803000000003</v>
@@ -7696,6 +7422,7 @@
         <v>6.6480034663453091E-2</v>
       </c>
       <c r="M58" s="4">
+        <f t="shared" si="0"/>
         <v>4.7327919094068305E-2</v>
       </c>
       <c r="N58" s="4">
@@ -7723,7 +7450,7 @@
         <v>99.7</v>
       </c>
       <c r="V58" s="5">
-        <v>4.4999999999999998E-2</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="W58" s="4">
         <v>263.81353000000001</v>
@@ -7791,6 +7518,7 @@
         <v>3.3684099201522821E-2</v>
       </c>
       <c r="M59" s="4">
+        <f t="shared" si="0"/>
         <v>-5.9575637974149664E-2</v>
       </c>
       <c r="N59" s="4">
@@ -7818,7 +7546,7 @@
         <v>101.6</v>
       </c>
       <c r="V59" s="5">
-        <v>3.6000000000000004E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W59" s="4">
         <v>262.23390999999998</v>
@@ -7886,6 +7614,7 @@
         <v>4.596749494317165E-2</v>
       </c>
       <c r="M60" s="4">
+        <f t="shared" si="0"/>
         <v>5.8175716534045518E-2</v>
       </c>
       <c r="N60" s="4">
@@ -7913,7 +7642,7 @@
         <v>101.9</v>
       </c>
       <c r="V60" s="5">
-        <v>3.6000000000000004E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W60" s="4">
         <v>261.62993999999998</v>
@@ -7981,6 +7710,7 @@
         <v>3.2978957787328733E-2</v>
       </c>
       <c r="M61" s="4">
+        <f t="shared" si="0"/>
         <v>3.9460936435610661E-2</v>
       </c>
       <c r="N61" s="4">
@@ -8008,7 +7738,7 @@
         <v>100.7</v>
       </c>
       <c r="V61" s="5">
-        <v>3.9E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W61" s="4">
         <v>263.67970000000003</v>
@@ -8076,6 +7806,7 @@
         <v>1.1472969657315701E-2</v>
       </c>
       <c r="M62" s="4">
+        <f t="shared" si="0"/>
         <v>-1.9867983674539458E-2</v>
       </c>
       <c r="N62" s="4">
@@ -8103,7 +7834,7 @@
         <v>100.7</v>
       </c>
       <c r="V62" s="5">
-        <v>4.0999999999999995E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W62" s="4">
         <v>262.01373999999998</v>
@@ -8171,6 +7902,7 @@
         <v>2.1726537248783817E-2</v>
       </c>
       <c r="M63" s="4">
+        <f t="shared" si="0"/>
         <v>-2.0631040912906795E-2</v>
       </c>
       <c r="N63" s="4">
@@ -8198,7 +7930,7 @@
         <v>98.4</v>
       </c>
       <c r="V63" s="5">
-        <v>4.0999999999999995E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W63" s="4">
         <v>263.77604000000002</v>
@@ -8266,6 +7998,7 @@
         <v>3.5082222412780917E-2</v>
       </c>
       <c r="M64" s="4">
+        <f t="shared" si="0"/>
         <v>6.117913006538922E-2</v>
       </c>
       <c r="N64" s="4">
@@ -8293,7 +8026,7 @@
         <v>100.9</v>
       </c>
       <c r="V64" s="5">
-        <v>4.0999999999999995E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W64" s="4">
         <v>268.13073000000003</v>
@@ -8361,6 +8094,7 @@
         <v>5.3189839245698867E-2</v>
       </c>
       <c r="M65" s="4">
+        <f t="shared" si="0"/>
         <v>-9.6968353932704865E-3</v>
       </c>
       <c r="N65" s="4">
@@ -8388,7 +8122,7 @@
         <v>103.6</v>
       </c>
       <c r="V65" s="5">
-        <v>4.0999999999999995E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W65" s="4">
         <v>272.15634999999997</v>
@@ -8456,6 +8190,7 @@
         <v>7.212811011116993E-2</v>
       </c>
       <c r="M66" s="4">
+        <f t="shared" si="0"/>
         <v>-3.4785558831915586E-2</v>
       </c>
       <c r="N66" s="4">
@@ -8483,7 +8218,7 @@
         <v>100.8</v>
       </c>
       <c r="V66" s="5">
-        <v>4.0999999999999995E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W66" s="4">
         <v>272.35588000000001</v>
@@ -8551,6 +8286,7 @@
         <v>0.10825055336608536</v>
       </c>
       <c r="M67" s="4">
+        <f t="shared" ref="M67:M75" si="1">X67/X66-1</f>
         <v>-3.0303143614614614E-2</v>
       </c>
       <c r="N67" s="4">
@@ -8578,7 +8314,7 @@
         <v>100</v>
       </c>
       <c r="V67" s="5">
-        <v>4.0999999999999995E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W67" s="4">
         <v>274.80014999999997</v>
@@ -8646,6 +8382,7 @@
         <v>9.8707903031458377E-2</v>
       </c>
       <c r="M68" s="4">
+        <f t="shared" si="1"/>
         <v>-1.4313974248728378E-2</v>
       </c>
       <c r="N68" s="4">
@@ -8668,10 +8405,10 @@
         <v>5.885614693416974E-2</v>
       </c>
       <c r="U68" s="4">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="V68" s="5">
-        <v>0.04</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W68" s="4">
         <v>274.39028999999999</v>
@@ -8739,6 +8476,7 @@
         <v>7.1000150931509909E-2</v>
       </c>
       <c r="M69" s="4">
+        <f t="shared" si="1"/>
         <v>-3.9215226023512018E-2</v>
       </c>
       <c r="N69" s="4">
@@ -8764,7 +8502,7 @@
         <v>100.7</v>
       </c>
       <c r="V69" s="5">
-        <v>4.0999999999999995E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W69" s="4">
         <v>279.84699000000001</v>
@@ -8832,6 +8570,7 @@
         <v>2.1606025691078612E-2</v>
       </c>
       <c r="M70" s="4">
+        <f t="shared" si="1"/>
         <v>-2.2973154553709296E-2</v>
       </c>
       <c r="N70" s="4">
@@ -8854,10 +8593,10 @@
         <v>5.885614693416974E-2</v>
       </c>
       <c r="U70" s="4">
-        <v>88.4</v>
+        <v>88.2</v>
       </c>
       <c r="V70" s="5">
-        <v>3.7999999999999999E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W70" s="4">
         <v>277.94519000000003</v>
@@ -8925,6 +8664,7 @@
         <v>3.5521536730100278E-2</v>
       </c>
       <c r="M71" s="4">
+        <f t="shared" si="1"/>
         <v>4.9127106176729329E-2</v>
       </c>
       <c r="N71" s="4">
@@ -8947,11 +8687,11 @@
         <v>6.3875404888089848E-2</v>
       </c>
       <c r="U71" s="4">
-        <v>89.4</v>
+        <v>91.2</v>
       </c>
       <c r="V71" s="10">
-        <f>AVERAGE(V68:V70)</f>
-        <v>3.9666666666666663E-2</v>
+        <f t="shared" ref="V71:V80" si="2">V70</f>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W71" s="4">
         <v>280.24891000000002</v>
@@ -9019,6 +8759,7 @@
         <v>5.4301903913044791E-2</v>
       </c>
       <c r="M72" s="4">
+        <f t="shared" si="1"/>
         <v>6.1214680400578647E-3</v>
       </c>
       <c r="N72" s="4">
@@ -9041,11 +8782,11 @@
         <v>6.3875404888089848E-2</v>
       </c>
       <c r="U72" s="4">
-        <v>90.4</v>
+        <v>95.2</v>
       </c>
       <c r="V72" s="10">
-        <f>AVERAGE(V69:V71)</f>
-        <v>3.9555555555555545E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W72" s="4">
         <v>283.41755000000001</v>
@@ -9113,6 +8854,7 @@
         <v>3.9623470388244542E-2</v>
       </c>
       <c r="M73" s="4">
+        <f t="shared" si="1"/>
         <v>-2.0396560301329081E-2</v>
       </c>
       <c r="N73" s="4">
@@ -9135,11 +8877,11 @@
         <v>6.3875404888089848E-2</v>
       </c>
       <c r="U73" s="4">
-        <v>90.4</v>
+        <v>93.4</v>
       </c>
       <c r="V73" s="10">
-        <f>AVERAGE(V70:V72)</f>
-        <v>3.9074074074074067E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W73" s="4">
         <v>283.58508999999998</v>
@@ -9207,12 +8949,12 @@
         <v>6.6834421150002266E-2</v>
       </c>
       <c r="M74" s="4">
+        <f t="shared" si="1"/>
         <v>3.0425775456245585E-2</v>
       </c>
       <c r="N74" s="4">
         <v>11.41</v>
       </c>
-      <c r="O74" s="4"/>
       <c r="P74" s="4">
         <v>7.716812447485788E-3</v>
       </c>
@@ -9229,11 +8971,11 @@
         <v>5.551985603420162E-2</v>
       </c>
       <c r="U74" s="4">
-        <v>90.4</v>
+        <v>93.8</v>
       </c>
       <c r="V74" s="10">
-        <f>AVERAGE(V71:V73)</f>
-        <v>3.9432098765432091E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="W74" s="4">
         <v>287.01436000000001</v>
@@ -9261,6 +9003,499 @@
       </c>
       <c r="AE74" s="5">
         <v>4.7300000000000002E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A75" s="3">
+        <v>45808</v>
+      </c>
+      <c r="B75" s="4">
+        <v>2.64E-2</v>
+      </c>
+      <c r="C75" s="4">
+        <v>2.247E-2</v>
+      </c>
+      <c r="D75" s="4">
+        <v>2.3349999999999999E-2</v>
+      </c>
+      <c r="E75" s="4">
+        <v>2.5049999999999999E-2</v>
+      </c>
+      <c r="F75" s="4">
+        <v>2.7719999999999998E-2</v>
+      </c>
+      <c r="G75" s="4">
+        <v>3.3940277777777778E-2</v>
+      </c>
+      <c r="H75" s="4">
+        <v>2.6017999999999999E-2</v>
+      </c>
+      <c r="I75" s="4">
+        <v>2.5194000000000001E-2</v>
+      </c>
+      <c r="J75" s="4">
+        <v>3.1591999999999995E-2</v>
+      </c>
+      <c r="K75" s="4">
+        <v>2.5748000000000004E-2</v>
+      </c>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4">
+        <f>X75/X74-1</f>
+        <v>5.5174625773974029E-2</v>
+      </c>
+      <c r="N75" s="4"/>
+      <c r="P75" s="4">
+        <f>Y75/Y74-1</f>
+        <v>5.5136058584011716E-2</v>
+      </c>
+      <c r="T75" s="4">
+        <v>5.551985603420162E-2</v>
+      </c>
+      <c r="U75" s="1">
+        <v>101.8</v>
+      </c>
+      <c r="V75" s="10">
+        <f t="shared" si="2"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="W75" s="4">
+        <v>285.30180000000001</v>
+      </c>
+      <c r="X75" s="4">
+        <v>2697.67</v>
+      </c>
+      <c r="Y75" s="4">
+        <v>879.49599999999998</v>
+      </c>
+      <c r="Z75" s="4">
+        <v>328.57400000000001</v>
+      </c>
+      <c r="AA75" s="5">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="AB75" s="5">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="AC75" s="5">
+        <v>3.2799999999999996E-2</v>
+      </c>
+      <c r="AD75" s="1">
+        <v>4.6199999999999998E-2</v>
+      </c>
+      <c r="AE75" s="1">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A76" s="3">
+        <v>45838</v>
+      </c>
+      <c r="B76" s="4">
+        <v>2.5699999999999997E-2</v>
+      </c>
+      <c r="C76" s="4">
+        <v>2.3179999999999999E-2</v>
+      </c>
+      <c r="D76" s="4">
+        <v>2.4550000000000002E-2</v>
+      </c>
+      <c r="E76" s="4">
+        <v>2.5920000000000002E-2</v>
+      </c>
+      <c r="F76" s="4">
+        <v>2.8069999999999998E-2</v>
+      </c>
+      <c r="G76" s="4">
+        <v>3.3713888888888897E-2</v>
+      </c>
+      <c r="H76" s="4">
+        <v>2.6629E-2</v>
+      </c>
+      <c r="I76" s="4">
+        <v>2.5838999999999997E-2</v>
+      </c>
+      <c r="J76" s="4">
+        <v>3.1327000000000001E-2</v>
+      </c>
+      <c r="K76" s="4">
+        <v>2.6516000000000001E-2</v>
+      </c>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4">
+        <f t="shared" ref="M76:M80" si="3">X76/X75-1</f>
+        <v>0.13864927882209455</v>
+      </c>
+      <c r="N76" s="4"/>
+      <c r="P76" s="4">
+        <f t="shared" ref="P76:P80" si="4">Y76/Y75-1</f>
+        <v>4.3657958649044426E-2</v>
+      </c>
+      <c r="T76" s="4">
+        <v>5.551985603420162E-2</v>
+      </c>
+      <c r="U76" s="1">
+        <v>108.7</v>
+      </c>
+      <c r="V76" s="10">
+        <f t="shared" si="2"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="W76" s="4">
+        <v>284.25313999999997</v>
+      </c>
+      <c r="X76" s="4">
+        <v>3071.7</v>
+      </c>
+      <c r="Y76" s="4">
+        <v>917.89300000000003</v>
+      </c>
+      <c r="Z76" s="4">
+        <v>331.233</v>
+      </c>
+      <c r="AA76" s="5">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="AB76" s="5">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AC76" s="5">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="AD76" s="1">
+        <v>4.4199999999999996E-2</v>
+      </c>
+      <c r="AE76" s="1">
+        <v>4.5899999999999996E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A77" s="3">
+        <v>45869</v>
+      </c>
+      <c r="B77" s="4">
+        <v>2.52E-2</v>
+      </c>
+      <c r="C77" s="4">
+        <v>2.2789999999999998E-2</v>
+      </c>
+      <c r="D77" s="4">
+        <v>2.4580000000000001E-2</v>
+      </c>
+      <c r="E77" s="4">
+        <v>2.5910000000000002E-2</v>
+      </c>
+      <c r="F77" s="4">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="G77" s="4">
+        <v>3.3620833333333343E-2</v>
+      </c>
+      <c r="H77" s="4">
+        <v>2.6371000000000002E-2</v>
+      </c>
+      <c r="I77" s="4">
+        <v>2.5423000000000001E-2</v>
+      </c>
+      <c r="J77" s="4">
+        <v>3.0939000000000001E-2</v>
+      </c>
+      <c r="K77" s="4">
+        <v>2.6196999999999998E-2</v>
+      </c>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4">
+        <f t="shared" si="3"/>
+        <v>5.6561513168603694E-2</v>
+      </c>
+      <c r="N77" s="4"/>
+      <c r="P77" s="4">
+        <f t="shared" si="4"/>
+        <v>1.2775998945410816E-2</v>
+      </c>
+      <c r="T77" s="4">
+        <v>5.5936460639536278E-2</v>
+      </c>
+      <c r="U77" s="1">
+        <v>110.8</v>
+      </c>
+      <c r="V77" s="10">
+        <f t="shared" si="2"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="W77" s="4">
+        <v>285.39897000000002</v>
+      </c>
+      <c r="X77" s="4">
+        <v>3245.44</v>
+      </c>
+      <c r="Y77" s="4">
+        <v>929.62</v>
+      </c>
+      <c r="Z77" s="4">
+        <v>331.51100000000002</v>
+      </c>
+      <c r="AA77" s="5">
+        <v>3.8399999999999997E-2</v>
+      </c>
+      <c r="AB77" s="5">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="AC77" s="5">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="AD77" s="1">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="AE77" s="1">
+        <v>4.6600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A78" s="3">
+        <v>45900</v>
+      </c>
+      <c r="B78" s="4">
+        <v>2.5099999999999997E-2</v>
+      </c>
+      <c r="C78" s="4">
+        <v>2.2460000000000001E-2</v>
+      </c>
+      <c r="D78" s="4">
+        <v>2.427E-2</v>
+      </c>
+      <c r="E78" s="4">
+        <v>2.581E-2</v>
+      </c>
+      <c r="F78" s="4">
+        <v>2.8130000000000002E-2</v>
+      </c>
+      <c r="G78" s="4">
+        <v>3.3371111111111122E-2</v>
+      </c>
+      <c r="H78" s="4">
+        <v>2.6335000000000001E-2</v>
+      </c>
+      <c r="I78" s="4">
+        <v>2.5184000000000002E-2</v>
+      </c>
+      <c r="J78" s="4">
+        <v>3.0592000000000001E-2</v>
+      </c>
+      <c r="K78" s="4">
+        <v>2.58E-2</v>
+      </c>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4">
+        <f t="shared" si="3"/>
+        <v>-1.8311846775783791E-2</v>
+      </c>
+      <c r="N78" s="4"/>
+      <c r="P78" s="4">
+        <f t="shared" si="4"/>
+        <v>2.3609646952518215E-2</v>
+      </c>
+      <c r="T78" s="4">
+        <v>5.5936460639536278E-2</v>
+      </c>
+      <c r="U78" s="1">
+        <v>111.4</v>
+      </c>
+      <c r="V78" s="10">
+        <f t="shared" si="2"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="W78" s="4">
+        <v>285.56625000000003</v>
+      </c>
+      <c r="X78" s="4">
+        <v>3186.01</v>
+      </c>
+      <c r="Y78" s="4">
+        <v>951.56799999999998</v>
+      </c>
+      <c r="Z78" s="4">
+        <v>333.63</v>
+      </c>
+      <c r="AA78" s="5">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="AB78" s="5">
+        <v>4.41E-2</v>
+      </c>
+      <c r="AC78" s="5">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="AD78" s="1">
+        <v>4.2699999999999995E-2</v>
+      </c>
+      <c r="AE78" s="1">
+        <v>4.4199999999999996E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A79" s="3">
+        <v>45930</v>
+      </c>
+      <c r="B79" s="4">
+        <v>2.5859999999999998E-2</v>
+      </c>
+      <c r="C79" s="4">
+        <v>2.3050000000000001E-2</v>
+      </c>
+      <c r="D79" s="4">
+        <v>2.5819999999999999E-2</v>
+      </c>
+      <c r="E79" s="4">
+        <v>2.7320000000000001E-2</v>
+      </c>
+      <c r="F79" s="4">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="G79" s="4">
+        <v>3.3053888888888897E-2</v>
+      </c>
+      <c r="H79" s="4">
+        <v>2.7397999999999999E-2</v>
+      </c>
+      <c r="I79" s="4">
+        <v>2.6331000000000004E-2</v>
+      </c>
+      <c r="J79" s="4">
+        <v>3.04E-2</v>
+      </c>
+      <c r="K79" s="4">
+        <v>2.7293999999999999E-2</v>
+      </c>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4">
+        <f t="shared" si="3"/>
+        <v>7.4886770600217645E-2</v>
+      </c>
+      <c r="N79" s="4"/>
+      <c r="P79" s="4">
+        <f t="shared" si="4"/>
+        <v>3.4903443579439308E-2</v>
+      </c>
+      <c r="T79" s="4">
+        <v>5.5936460639536278E-2</v>
+      </c>
+      <c r="U79" s="1">
+        <v>110.1</v>
+      </c>
+      <c r="V79" s="10">
+        <f t="shared" si="2"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="W79" s="4">
+        <v>284.53291999999999</v>
+      </c>
+      <c r="X79" s="4">
+        <v>3424.6</v>
+      </c>
+      <c r="Y79" s="4">
+        <v>984.78099999999995</v>
+      </c>
+      <c r="Z79" s="4">
+        <v>336.52300000000002</v>
+      </c>
+      <c r="AA79" s="5">
+        <v>3.7200000000000004E-2</v>
+      </c>
+      <c r="AB79" s="5">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="AC79" s="5">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="AD79" s="1">
+        <v>4.2199999999999994E-2</v>
+      </c>
+      <c r="AE79" s="1">
+        <v>4.4199999999999996E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A80" s="3">
+        <v>45961</v>
+      </c>
+      <c r="B80" s="4">
+        <v>2.6889999999999997E-2</v>
+      </c>
+      <c r="C80" s="4">
+        <v>2.4080000000000001E-2</v>
+      </c>
+      <c r="D80" s="4">
+        <v>2.6749999999999999E-2</v>
+      </c>
+      <c r="E80" s="4">
+        <v>2.7949999999999999E-2</v>
+      </c>
+      <c r="F80" s="4">
+        <v>2.98E-2</v>
+      </c>
+      <c r="G80" s="4">
+        <v>3.2707500000000007E-2</v>
+      </c>
+      <c r="H80" s="4">
+        <v>2.8618000000000001E-2</v>
+      </c>
+      <c r="I80" s="4">
+        <v>2.7450000000000002E-2</v>
+      </c>
+      <c r="J80" s="4">
+        <v>3.0114999999999999E-2</v>
+      </c>
+      <c r="K80" s="4">
+        <v>2.8320999999999999E-2</v>
+      </c>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4">
+        <f t="shared" si="3"/>
+        <v>0.19941015009052165</v>
+      </c>
+      <c r="N80" s="4"/>
+      <c r="P80" s="4">
+        <f t="shared" si="4"/>
+        <v>2.1782507989085875E-2</v>
+      </c>
+      <c r="T80" s="10">
+        <f>AVERAGE(T68:T79)</f>
+        <v>5.8546967123999372E-2</v>
+      </c>
+      <c r="U80" s="1">
+        <v>109.8</v>
+      </c>
+      <c r="V80" s="10">
+        <f t="shared" si="2"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="W80" s="4">
+        <v>282.72926000000001</v>
+      </c>
+      <c r="X80" s="4">
+        <v>4107.5</v>
+      </c>
+      <c r="Y80" s="4">
+        <v>1006.232</v>
+      </c>
+      <c r="Z80" s="4">
+        <v>339.233</v>
+      </c>
+      <c r="AA80" s="5">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="AB80" s="5">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="AC80" s="5">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="AD80" s="1">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="AE80" s="1">
+        <v>4.41E-2</v>
       </c>
     </row>
   </sheetData>
